--- a/data/sources/2026/2026_Complementary_Studies_Course_Details.xlsx
+++ b/data/sources/2026/2026_Complementary_Studies_Course_Details.xlsx
@@ -407,7 +407,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CourseMeetings" displayName="CourseMeetings" ref="A2:G178" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CourseMeetings" displayName="CourseMeetings" ref="A2:G177" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="7">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Kind"/>
@@ -9987,7 +9987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14569,27 +14569,7 @@
       <c r="F177" s="14" t="n"/>
       <c r="G177" s="14" t="n"/>
     </row>
-    <row r="178" ht="23" customHeight="1">
-      <c r="A178" s="14" t="inlineStr">
-        <is>
-          <t>SLL1069F</t>
-        </is>
-      </c>
-      <c r="B178" s="14" t="inlineStr">
-        <is>
-          <t>tutorial</t>
-        </is>
-      </c>
-      <c r="C178" s="14" t="inlineStr">
-        <is>
-          <t>thu,fri</t>
-        </is>
-      </c>
-      <c r="D178" s="16" t="n"/>
-      <c r="E178" s="16" t="n"/>
-      <c r="F178" s="14" t="n"/>
-      <c r="G178" s="14" t="n"/>
-    </row>
+    <row r="178" ht="23" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
